--- a/image source/lunch_record.xlsx
+++ b/image source/lunch_record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Desktop\Project\kinder-track\image source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6C5335-C189-45CD-B660-41374A87B9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB209F4-94F0-49FB-91CB-12AB33C2677D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกอาหารกลางวัน" sheetId="1" r:id="rId1"/>
@@ -402,36 +402,36 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,150 +751,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
     </row>
     <row r="2" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
     </row>
     <row r="3" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="23" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="24" t="s">
+      <c r="AK3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="22" t="s">
+      <c r="AL3" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="2">
         <v>1</v>
       </c>
@@ -988,9 +988,9 @@
       <c r="AI4" s="2">
         <v>31</v>
       </c>
-      <c r="AJ4" s="20"/>
-      <c r="AK4" s="20"/>
-      <c r="AL4" s="20"/>
+      <c r="AJ4" s="23"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
     </row>
     <row r="5" spans="1:38" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -2913,12 +2913,12 @@
       <c r="AL44" s="8"/>
     </row>
     <row r="45" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="9">
         <f t="shared" ref="E45:AI45" si="2">COUNTIF(E5:E44,"ห")</f>
         <v>0</v>
@@ -3054,32 +3054,32 @@
       <c r="AL45" s="10"/>
     </row>
     <row r="47" spans="1:38" ht="22.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
       <c r="E47" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="27" t="e">
+      <c r="F47" s="26" t="e">
         <f>รับประทานอาหารกลางวัน</f>
         <v>#NAME?</v>
       </c>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
       <c r="J47" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K47" s="27" t="e">
+      <c r="K47" s="26" t="e">
         <f>ไม่รับประทาน / ขาดเรียน</f>
         <v>#NAME?</v>
       </c>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3120,46 +3120,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" spans="1:17" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -5274,24 +5274,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
